--- a/data/samples/demo-empty.xlsx
+++ b/data/samples/demo-empty.xlsx
@@ -2,23 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="orders" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="packages" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="vehicles" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="zones" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'orders'!$A$1:$K$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'packages'!$A$1:$C$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'vehicles'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'zones'!$A$1:$I$6</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
 </workbook>
 </file>
 
@@ -28,10 +18,8 @@
   <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,24 +31,18 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -175,72 +157,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -296,7 +220,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -305,13 +229,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -345,17 +269,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -410,8 +323,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -424,7 +335,7 @@
   <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,8 +396,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K51"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -499,7 +409,7 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,8 +430,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C100"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -534,7 +443,7 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,8 +489,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -594,7 +502,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,7 +553,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>